--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_PSC.xlsx
@@ -13,8 +13,8 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -458,7 +458,11 @@
           <t>team_name</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -468,36 +472,72 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>primary_scorer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Rosado | M. Landdeck (-29.0 net)</t>
+          <t>G. Rosado (20.5 ppg)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>most_used_player</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>G. Rosado (31.6 mpg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>best_3pt_pct</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>T. Coleman (100.0%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>G. Rosado | M. Landdeck (-30.2 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>G. Rosado | M. Landdeck | T. Coleman (-33.4 net)</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>D. Fragoso | G. Rosado | M. Landdeck (-18.9 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -508,28 +548,627 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:U7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="15" max="15"/>
+    <col width="10" customWidth="1" min="16" max="16"/>
+    <col width="10" customWidth="1" min="17" max="17"/>
+    <col width="10" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="23" customWidth="1" min="20" max="20"/>
+    <col width="41" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>player_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>playing_position</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>games_started</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes_total</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>mpg</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>ppg</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rpg</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>apg</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>tov_pg</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>spg</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>bpg</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>fg_pct</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>tp_pct</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>ft_pct</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>efg_pct</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>ts_pct</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>plus_minus_pg</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>on_off_net_diff_per40</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>role_tag</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>G. Rosado</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>63.2</v>
+      </c>
+      <c r="G2" t="n">
+        <v>31.6</v>
+      </c>
+      <c r="H2" t="n">
+        <v>20.5</v>
+      </c>
+      <c r="I2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>90.0%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>72.7%</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>77.7%</t>
+        </is>
+      </c>
+      <c r="S2" t="n">
+        <v>-22</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-30.2</v>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer, efficient</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>M. Landdeck</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>29.4</v>
+      </c>
+      <c r="H3" t="n">
+        <v>12</v>
+      </c>
+      <c r="I3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>23.1%</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>37.3%</t>
+        </is>
+      </c>
+      <c r="S3" t="n">
+        <v>-18.5</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-8.800000000000001</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>high-minutes, primary-scorer</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>D. Fragoso</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>26.7</v>
+      </c>
+      <c r="H4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I4" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>1</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>26.7%</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>35.4%</t>
+        </is>
+      </c>
+      <c r="S4" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="T4" t="n">
+        <v>17.2</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>high-minutes, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H. Sotta</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>49</v>
+      </c>
+      <c r="G5" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>2</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>25.0%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="S5" t="n">
+        <v>-9</v>
+      </c>
+      <c r="T5" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>high-minutes, impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>T. Coleman</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="G6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>63.3%</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>63.3%</t>
+        </is>
+      </c>
+      <c r="S6" t="n">
+        <v>-12.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>efficient, shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>45.5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>22.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>41.7%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="S7" t="n">
+        <v>-12</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-3.1</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>efficient, shooter</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:U7"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -578,7 +1217,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="39" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -661,22 +1300,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>24.9</v>
+        <v>49</v>
       </c>
       <c r="H2" t="n">
-        <v>72.40000000000001</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>101.3</v>
+        <v>102.1</v>
       </c>
       <c r="J2" t="n">
-        <v>-29</v>
+        <v>-30.2</v>
       </c>
     </row>
     <row r="3">
@@ -697,26 +1336,26 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>L. Rahama | M. Landdeck</t>
+          <t>D. Fragoso | G. Rosado</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G3" t="n">
-        <v>18.7</v>
+        <v>42</v>
       </c>
       <c r="H3" t="n">
-        <v>81.3</v>
+        <v>71.5</v>
       </c>
       <c r="I3" t="n">
-        <v>81.3</v>
+        <v>85.7</v>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="4">
@@ -737,26 +1376,26 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>L. Rahama | M. Landdeck</t>
+          <t>D. Fragoso | G. Rosado</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G4" t="n">
-        <v>18.7</v>
+        <v>42</v>
       </c>
       <c r="H4" t="n">
-        <v>81.3</v>
+        <v>71.5</v>
       </c>
       <c r="I4" t="n">
-        <v>81.3</v>
+        <v>85.7</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="5">
@@ -777,26 +1416,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>G. Rosado | M. Landdeck | T. Coleman</t>
+          <t>D. Fragoso | G. Rosado | M. Landdeck</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G5" t="n">
-        <v>18</v>
+        <v>33.8</v>
       </c>
       <c r="H5" t="n">
-        <v>64.59999999999999</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>98</v>
+        <v>93.5</v>
       </c>
       <c r="J5" t="n">
-        <v>-33.4</v>
+        <v>-18.9</v>
       </c>
     </row>
     <row r="6">
@@ -817,26 +1456,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>L. Rahama | M. Landdeck | T. Coleman</t>
+          <t>D. Fragoso | G. Rosado | H. Sotta</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F6" t="n">
         <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>16.3</v>
+        <v>23</v>
       </c>
       <c r="H6" t="n">
-        <v>78.59999999999999</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>88.40000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="J6" t="n">
-        <v>-9.800000000000001</v>
+        <v>-15.7</v>
       </c>
     </row>
     <row r="7">
@@ -857,26 +1496,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>L. Rahama | M. Landdeck | T. Coleman</t>
+          <t>D. Fragoso | M. Landdeck | T. Coleman</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
         <v>7</v>
       </c>
       <c r="G7" t="n">
-        <v>16.3</v>
+        <v>22.8</v>
       </c>
       <c r="H7" t="n">
-        <v>78.59999999999999</v>
+        <v>61.5</v>
       </c>
       <c r="I7" t="n">
-        <v>88.40000000000001</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>-9.800000000000001</v>
+        <v>-21.1</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_PSC.xlsx
@@ -13,9 +13,9 @@
     <sheet name="duos_trios" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$7</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$A$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Rosado (20.5 ppg)</t>
+          <t>G. Rosado (19 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G. Rosado (31.6 mpg)</t>
+          <t>G. Rosado (32.8 mpg)</t>
         </is>
       </c>
     </row>
@@ -515,29 +515,53 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>best_duo</t>
+          <t>base_lineup</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G. Rosado | M. Landdeck (-30.2 net)</t>
+          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (15.3 min)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>best_lineup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (-23.5 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>best_duo</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>G. Rosado | M. Landdeck (-19.7 net)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>best_trio</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>D. Fragoso | G. Rosado | M. Landdeck (-18.9 net)</t>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>G. Rosado | M. Landdeck | T. Coleman (-22.8 net)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:B9"/>
+  <autoFilter ref="A1:B11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -548,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -698,38 +722,38 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>63.2</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>31.6</v>
+        <v>32.8</v>
       </c>
       <c r="H2" t="n">
-        <v>20.5</v>
+        <v>19</v>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -739,24 +763,24 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>77.7%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-22</v>
+        <v>-15.3</v>
       </c>
       <c r="T2" t="n">
-        <v>-30.2</v>
+        <v>-14.6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -781,65 +805,65 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>58.7</v>
+        <v>91.2</v>
       </c>
       <c r="G3" t="n">
-        <v>29.4</v>
+        <v>30.4</v>
       </c>
       <c r="H3" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="I3" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>26.9%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>68.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-18.5</v>
+        <v>-12.7</v>
       </c>
       <c r="T3" t="n">
-        <v>-8.800000000000001</v>
+        <v>-0.5</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -855,78 +879,78 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>D. Fragoso</t>
+          <t>T. Coleman</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="G4" t="n">
+        <v>25.4</v>
+      </c>
+      <c r="H4" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>7.7</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>26.7</v>
-      </c>
-      <c r="H4" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I4" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>1</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-12.5</v>
+        <v>-10</v>
       </c>
       <c r="T4" t="n">
-        <v>17.2</v>
+        <v>-3.1</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, impact</t>
+          <t>high-minutes, efficient, shooter</t>
         </is>
       </c>
     </row>
@@ -938,74 +962,78 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H. Sotta</t>
+          <t>D. Fragoso</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>24.5</v>
+        <v>23.4</v>
       </c>
       <c r="H5" t="n">
-        <v>3.5</v>
+        <v>5.7</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>3.3</v>
       </c>
       <c r="J5" t="n">
         <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>25.0%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr"/>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="S5" t="n">
         <v>-9</v>
       </c>
       <c r="T5" t="n">
-        <v>21.7</v>
+        <v>7.5</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>high-minutes, impact</t>
+          <t>impact</t>
         </is>
       </c>
     </row>
@@ -1017,74 +1045,74 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>T. Coleman</t>
+          <t>H. Sotta</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>46.6</v>
+        <v>64.2</v>
       </c>
       <c r="G6" t="n">
-        <v>23.3</v>
+        <v>21.4</v>
       </c>
       <c r="H6" t="n">
-        <v>9.5</v>
+        <v>2.3</v>
       </c>
       <c r="I6" t="n">
-        <v>9.5</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>63.3%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-12.5</v>
+        <v>-6.3</v>
       </c>
       <c r="T6" t="n">
-        <v>-2</v>
+        <v>10.9</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>efficient, shooter</t>
+          <t>impact</t>
         </is>
       </c>
     </row>
@@ -1096,79 +1124,324 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
+          <t>J. Grewal</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" t="n">
+        <v>3</v>
+      </c>
+      <c r="F7" t="n">
+        <v>60.3</v>
+      </c>
+      <c r="G7" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J7" t="n">
+        <v>4</v>
+      </c>
+      <c r="K7" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>45.5</v>
-      </c>
-      <c r="G7" t="n">
-        <v>22.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>50.0%</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr"/>
+          <t>27.3%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>-12</v>
+        <v>-10.3</v>
       </c>
       <c r="T7" t="n">
-        <v>-3.1</v>
+        <v>-9.9</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
+          <t>rotation</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>P. Bastos</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>52.1</v>
+      </c>
+      <c r="G8" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>38.5%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>57.7%</t>
+        </is>
+      </c>
+      <c r="S8" t="n">
+        <v>-8</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>shooter</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F9" t="n">
+        <v>44.9</v>
+      </c>
+      <c r="G9" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>30.0%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>33.3%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>35.0%</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="S9" t="n">
+        <v>-1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>impact</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>40.1</v>
+      </c>
+      <c r="G10" t="n">
+        <v>20</v>
+      </c>
+      <c r="H10" t="n">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>70.8%</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>70.4%</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>efficient, shooter</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U7"/>
+  <autoFilter ref="A1:U10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1179,28 +1452,219 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="11" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>info</t>
+          <t>categoria</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>team_name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>lineup_players</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>games</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>stints</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>minutes</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>pf_per40</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>pa_per40</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>net_per40</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>team_rank_minutes</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>team_rank_net</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>team_rank_defense</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sem dados</t>
-        </is>
+          <t>Base lineup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G2" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="I2" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K2" t="n">
+        <v>26</v>
+      </c>
+      <c r="L2" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Best lineup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="H3" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="I3" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="J3" t="n">
+        <v>1</v>
+      </c>
+      <c r="K3" t="n">
+        <v>26</v>
+      </c>
+      <c r="L3" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Best defense</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F4" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="G4" t="n">
+        <v>78.3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="I4" t="n">
+        <v>-23.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>26</v>
+      </c>
+      <c r="L4" t="n">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A2"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1217,7 +1681,7 @@
     <col width="10" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="17" customWidth="1" min="3" max="3"/>
-    <col width="39" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
@@ -1300,22 +1764,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="G2" t="n">
-        <v>49</v>
+        <v>77.3</v>
       </c>
       <c r="H2" t="n">
-        <v>71.90000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>102.1</v>
+        <v>96.7</v>
       </c>
       <c r="J2" t="n">
-        <v>-30.2</v>
+        <v>-19.7</v>
       </c>
     </row>
     <row r="3">
@@ -1340,22 +1804,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G3" t="n">
-        <v>42</v>
+        <v>57.1</v>
       </c>
       <c r="H3" t="n">
-        <v>71.5</v>
+        <v>74.3</v>
       </c>
       <c r="I3" t="n">
-        <v>85.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="4">
@@ -1380,22 +1844,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="G4" t="n">
-        <v>42</v>
+        <v>57.1</v>
       </c>
       <c r="H4" t="n">
-        <v>71.5</v>
+        <v>74.3</v>
       </c>
       <c r="I4" t="n">
-        <v>85.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>-14.3</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="5">
@@ -1416,26 +1880,26 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>D. Fragoso | G. Rosado | M. Landdeck</t>
+          <t>G. Rosado | M. Landdeck | T. Coleman</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G5" t="n">
-        <v>33.8</v>
+        <v>49.2</v>
       </c>
       <c r="H5" t="n">
-        <v>74.59999999999999</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="I5" t="n">
-        <v>93.5</v>
+        <v>91.8</v>
       </c>
       <c r="J5" t="n">
-        <v>-18.9</v>
+        <v>-22.8</v>
       </c>
     </row>
     <row r="6">
@@ -1456,26 +1920,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D. Fragoso | G. Rosado | H. Sotta</t>
+          <t>D. Fragoso | G. Rosado | M. Landdeck</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="H6" t="n">
-        <v>76.59999999999999</v>
+        <v>75.2</v>
       </c>
       <c r="I6" t="n">
-        <v>92.2</v>
+        <v>88.5</v>
       </c>
       <c r="J6" t="n">
-        <v>-15.7</v>
+        <v>-13.3</v>
       </c>
     </row>
     <row r="7">
@@ -1496,26 +1960,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D. Fragoso | M. Landdeck | T. Coleman</t>
+          <t>D. Fragoso | G. Rosado | M. Landdeck</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>22.8</v>
+        <v>42</v>
       </c>
       <c r="H7" t="n">
-        <v>61.5</v>
+        <v>75.2</v>
       </c>
       <c r="I7" t="n">
-        <v>82.59999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="J7" t="n">
-        <v>-21.1</v>
+        <v>-13.3</v>
       </c>
     </row>
   </sheetData>

--- a/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_PSC.xlsx
+++ b/site/leagues/betclic/2026_2027/xlsx/team_packs/team_pack_PSC.xlsx
@@ -15,7 +15,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'overview'!$A$1:$B$11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'rotation'!$A$1:$U$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'key_lineups'!$A$1:$L$5</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'duos_trios'!$A$1:$J$7</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +484,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>G. Rosado (19 ppg)</t>
+          <t>G. Rosado (17.8 ppg)</t>
         </is>
       </c>
     </row>
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>G. Rosado (32.8 mpg)</t>
+          <t>G. Rosado (34.0 mpg)</t>
         </is>
       </c>
     </row>
@@ -520,7 +520,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (15.3 min)</t>
+          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (16.2 min)</t>
         </is>
       </c>
     </row>
@@ -532,7 +532,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman (-23.5 net)</t>
+          <t>D. Fragoso | G. Rosado | M. Landdeck | P. Oliveira | T. Coleman (20.0 net)</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>G. Rosado | M. Landdeck (-19.7 net)</t>
+          <t>G. Rosado | M. Landdeck (-14.4 net)</t>
         </is>
       </c>
     </row>
@@ -556,7 +556,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>G. Rosado | M. Landdeck | T. Coleman (-22.8 net)</t>
+          <t>G. Rosado | M. Landdeck | T. Coleman (-13.5 net)</t>
         </is>
       </c>
     </row>
@@ -718,69 +718,69 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>98.40000000000001</v>
+        <v>135.8</v>
       </c>
       <c r="G2" t="n">
-        <v>32.8</v>
+        <v>34</v>
       </c>
       <c r="H2" t="n">
-        <v>19</v>
+        <v>17.8</v>
       </c>
       <c r="I2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K2" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>75.9%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>75.7%</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>-15.3</v>
+        <v>-11.8</v>
       </c>
       <c r="T2" t="n">
-        <v>-14.6</v>
+        <v>-8.6</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
@@ -801,69 +801,69 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>G</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>91.2</v>
+        <v>124.6</v>
       </c>
       <c r="G3" t="n">
-        <v>30.4</v>
+        <v>31.1</v>
       </c>
       <c r="H3" t="n">
-        <v>16</v>
+        <v>15.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>32.6%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>-12.7</v>
+        <v>-10</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
       <c r="U3" t="inlineStr">
         <is>
@@ -884,42 +884,42 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>F</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>76.09999999999999</v>
+        <v>102.5</v>
       </c>
       <c r="G4" t="n">
-        <v>25.4</v>
+        <v>25.6</v>
       </c>
       <c r="H4" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="I4" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M4" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -929,28 +929,28 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="S4" t="n">
-        <v>-10</v>
+        <v>-6.5</v>
       </c>
       <c r="T4" t="n">
-        <v>-3.1</v>
+        <v>0.4</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>high-minutes, efficient, shooter</t>
+          <t>high-minutes, shooter</t>
         </is>
       </c>
     </row>
@@ -971,38 +971,38 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" t="n">
-        <v>70.09999999999999</v>
+        <v>94</v>
       </c>
       <c r="G5" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="H5" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="I5" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
         <v>0</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1012,24 +1012,24 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="S5" t="n">
-        <v>-9</v>
+        <v>-6.8</v>
       </c>
       <c r="T5" t="n">
-        <v>7.5</v>
+        <v>6</v>
       </c>
       <c r="U5" t="inlineStr">
         <is>
@@ -1054,65 +1054,65 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>64.2</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>21.4</v>
+        <v>20.1</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="I6" t="n">
-        <v>5</v>
+        <v>5.8</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>30.0%</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>14.3%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>-6.3</v>
+        <v>-6.5</v>
       </c>
       <c r="T6" t="n">
-        <v>10.9</v>
+        <v>3.6</v>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>rotation</t>
         </is>
       </c>
     </row>
@@ -1133,43 +1133,43 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E7" t="n">
         <v>3</v>
       </c>
       <c r="F7" t="n">
-        <v>60.3</v>
+        <v>74.2</v>
       </c>
       <c r="G7" t="n">
-        <v>20.1</v>
+        <v>18.6</v>
       </c>
       <c r="H7" t="n">
-        <v>6.7</v>
+        <v>7.5</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>27.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1179,19 +1179,19 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>-10.3</v>
+        <v>-5.8</v>
       </c>
       <c r="T7" t="n">
-        <v>-9.9</v>
+        <v>-1.3</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -1207,74 +1207,74 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>P. Bastos</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>G</t>
-        </is>
-      </c>
+          <t>L. Rahama</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="n">
+        <v>4</v>
+      </c>
+      <c r="E8" t="n">
         <v>3</v>
       </c>
-      <c r="E8" t="n">
-        <v>0</v>
-      </c>
       <c r="F8" t="n">
-        <v>52.1</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>17.4</v>
+        <v>17.5</v>
       </c>
       <c r="H8" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="J8" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="K8" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>45.5%</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr"/>
+          <t>28.6%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>88.9%</t>
+        </is>
+      </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>57.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="S8" t="n">
-        <v>-8</v>
+        <v>-3</v>
       </c>
       <c r="T8" t="n">
-        <v>-7.6</v>
+        <v>8.5</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>shooter</t>
+          <t>impact</t>
         </is>
       </c>
     </row>
@@ -1286,74 +1286,78 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>L. Rahama</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>P. Oliveira</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="G9" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="H9" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="I9" t="n">
         <v>2</v>
       </c>
-      <c r="F9" t="n">
-        <v>44.9</v>
-      </c>
-      <c r="G9" t="n">
-        <v>15</v>
-      </c>
-      <c r="H9" t="n">
-        <v>7</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3</v>
-      </c>
       <c r="J9" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7</v>
+        <v>2</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>63.3%</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="S9" t="n">
-        <v>-1</v>
+        <v>-6.7</v>
       </c>
       <c r="T9" t="n">
-        <v>17.9</v>
+        <v>3</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>impact</t>
+          <t>efficient, shooter</t>
         </is>
       </c>
     </row>
@@ -1365,7 +1369,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>P. Oliveira</t>
+          <t>P. Bastos</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1374,69 +1378,65 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>40.1</v>
+        <v>52.1</v>
       </c>
       <c r="G10" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H10" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J10" t="n">
         <v>1.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>42.9%</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>60.0%</t>
-        </is>
-      </c>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>57.7%</t>
         </is>
       </c>
       <c r="S10" t="n">
-        <v>-8.5</v>
+        <v>-6</v>
       </c>
       <c r="T10" t="n">
-        <v>4.1</v>
+        <v>-11.4</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>efficient, shooter</t>
+          <t>shooter</t>
         </is>
       </c>
     </row>
@@ -1452,10 +1452,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="17" customWidth="1" min="2" max="2"/>
     <col width="45" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1548,31 +1548,31 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
-        <v>15.3</v>
+        <v>16.2</v>
       </c>
       <c r="G2" t="n">
-        <v>78.3</v>
+        <v>81.2</v>
       </c>
       <c r="H2" t="n">
-        <v>101.8</v>
+        <v>96</v>
       </c>
       <c r="I2" t="n">
-        <v>-23.5</v>
+        <v>-14.8</v>
       </c>
       <c r="J2" t="n">
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L2" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3">
@@ -1588,35 +1588,35 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman</t>
+          <t>D. Fragoso | G. Rosado | M. Landdeck | P. Oliveira | T. Coleman</t>
         </is>
       </c>
       <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F3" t="n">
+        <v>16</v>
+      </c>
+      <c r="G3" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="H3" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="I3" t="n">
+        <v>20</v>
+      </c>
+      <c r="J3" t="n">
         <v>2</v>
       </c>
-      <c r="E3" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="G3" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="I3" t="n">
-        <v>-23.5</v>
-      </c>
-      <c r="J3" t="n">
-        <v>1</v>
-      </c>
       <c r="K3" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -1632,39 +1632,83 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>G. Rosado | J. Grewal | L. Rahama | M. Landdeck | T. Coleman</t>
+          <t>D. Fragoso | G. Rosado | M. Landdeck | P. Oliveira | T. Coleman</t>
         </is>
       </c>
       <c r="D4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F4" t="n">
+        <v>16</v>
+      </c>
+      <c r="G4" t="n">
+        <v>72.59999999999999</v>
+      </c>
+      <c r="H4" t="n">
+        <v>52.6</v>
+      </c>
+      <c r="I4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="E4" t="n">
+      <c r="K4" t="n">
+        <v>11</v>
+      </c>
+      <c r="L4" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Rotation lineup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Portimonense SC</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>D. Fragoso | G. Rosado | L. Rahama | M. Landdeck | T. Coleman</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="F4" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="G4" t="n">
-        <v>78.3</v>
-      </c>
-      <c r="H4" t="n">
-        <v>101.8</v>
-      </c>
-      <c r="I4" t="n">
-        <v>-23.5</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
-      <c r="K4" t="n">
-        <v>26</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="E5" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="G5" t="n">
+        <v>82.7</v>
+      </c>
+      <c r="H5" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-12.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
         <v>22</v>
       </c>
+      <c r="L5" t="n">
+        <v>24</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L4"/>
+  <autoFilter ref="A1:L5"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1764,22 +1808,22 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>77.3</v>
+        <v>108.1</v>
       </c>
       <c r="H2" t="n">
-        <v>77.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="I2" t="n">
-        <v>96.7</v>
+        <v>89.90000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>-19.7</v>
+        <v>-14.4</v>
       </c>
     </row>
     <row r="3">
@@ -1804,22 +1848,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G3" t="n">
-        <v>57.1</v>
+        <v>79</v>
       </c>
       <c r="H3" t="n">
-        <v>74.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I3" t="n">
-        <v>83.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="J3" t="n">
-        <v>-9.1</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="4">
@@ -1844,22 +1888,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G4" t="n">
-        <v>57.1</v>
+        <v>79</v>
       </c>
       <c r="H4" t="n">
-        <v>74.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>83.40000000000001</v>
+        <v>79</v>
       </c>
       <c r="J4" t="n">
-        <v>-9.1</v>
+        <v>-7.1</v>
       </c>
     </row>
     <row r="5">
@@ -1884,22 +1928,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G5" t="n">
-        <v>49.2</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>69.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>91.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>-22.8</v>
+        <v>-13.5</v>
       </c>
     </row>
     <row r="6">
@@ -1920,26 +1964,26 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>D. Fragoso | G. Rosado | M. Landdeck</t>
+          <t>D. Fragoso | G. Rosado | T. Coleman</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F6" t="n">
         <v>12</v>
       </c>
       <c r="G6" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H6" t="n">
-        <v>75.2</v>
+        <v>72</v>
       </c>
       <c r="I6" t="n">
-        <v>88.5</v>
+        <v>76</v>
       </c>
       <c r="J6" t="n">
-        <v>-13.3</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="7">
@@ -1960,26 +2004,26 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>D. Fragoso | G. Rosado | M. Landdeck</t>
+          <t>D. Fragoso | G. Rosado | T. Coleman</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>12</v>
       </c>
       <c r="G7" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="H7" t="n">
-        <v>75.2</v>
+        <v>72</v>
       </c>
       <c r="I7" t="n">
-        <v>88.5</v>
+        <v>76</v>
       </c>
       <c r="J7" t="n">
-        <v>-13.3</v>
+        <v>-4</v>
       </c>
     </row>
   </sheetData>
